--- a/output/roomself_excel/7547.xlsx
+++ b/output/roomself_excel/7547.xlsx
@@ -498,10 +498,10 @@
         <v>2452</v>
       </c>
       <c r="E3" t="n">
-        <v>456</v>
+        <v>267</v>
       </c>
       <c r="F3" t="n">
-        <v>253</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
@@ -520,7 +520,7 @@
         <v>5564</v>
       </c>
       <c r="E4" t="n">
-        <v>1178</v>
+        <v>827</v>
       </c>
       <c r="F4" t="n">
         <v>618</v>
@@ -542,7 +542,7 @@
         <v>1884</v>
       </c>
       <c r="E5" t="n">
-        <v>580</v>
+        <v>327</v>
       </c>
       <c r="F5" t="n">
         <v>178</v>

--- a/output/roomself_excel/7547.xlsx
+++ b/output/roomself_excel/7547.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,77 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_5</t>
         </is>
       </c>
     </row>
@@ -475,12 +540,37 @@
       <c r="D2" t="n">
         <v>1340</v>
       </c>
-      <c r="E2" t="n">
-        <v>235</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>171</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="G2" t="n">
+        <v>54</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>181</v>
+      </c>
+      <c r="J2" t="n">
+        <v>17</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +587,29 @@
       <c r="D3" t="n">
         <v>2452</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>267</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>54</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +626,60 @@
       <c r="D4" t="n">
         <v>5564</v>
       </c>
-      <c r="E4" t="n">
-        <v>827</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>618</v>
+        <v>320</v>
+      </c>
+      <c r="G4" t="n">
+        <v>54</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>773</v>
+      </c>
+      <c r="J4" t="n">
+        <v>39</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>320</v>
+      </c>
+      <c r="M4" t="n">
+        <v>17</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>247</v>
+      </c>
+      <c r="P4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>281</v>
+      </c>
+      <c r="S4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +697,45 @@
       <c r="D5" t="n">
         <v>1884</v>
       </c>
-      <c r="E5" t="n">
-        <v>327</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>178</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="G5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>86</v>
+      </c>
+      <c r="J5" t="n">
+        <v>49</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>75</v>
+      </c>
+      <c r="M5" t="n">
+        <v>17</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
